--- a/data/dataset.xlsx
+++ b/data/dataset.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\coc-base-designer\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BEF8291-23D5-4770-B0D0-904A02C196EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457A0F5E-3BAF-4A02-8027-DB0BE3872C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{990ECCB1-38A2-40BE-9CA8-CCE9A9FAB587}"/>
   </bookViews>
   <sheets>
-    <sheet name="Town Hall" sheetId="7" r:id="rId1"/>
-    <sheet name="Wall" sheetId="6" r:id="rId2"/>
-    <sheet name="Mortar" sheetId="4" r:id="rId3"/>
-    <sheet name="Archer Tower" sheetId="3" r:id="rId4"/>
-    <sheet name="canon" sheetId="2" r:id="rId5"/>
+    <sheet name="Wizard Tower" sheetId="8" r:id="rId1"/>
+    <sheet name="Town Hall" sheetId="7" r:id="rId2"/>
+    <sheet name="Wall" sheetId="6" r:id="rId3"/>
+    <sheet name="Mortar" sheetId="4" r:id="rId4"/>
+    <sheet name="Archer Tower" sheetId="3" r:id="rId5"/>
+    <sheet name="canon" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="145">
   <si>
     <t>Town Hall Level</t>
   </si>
@@ -329,6 +330,9 @@
     <t>Wall</t>
   </si>
   <si>
+    <t>Cost</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -402,6 +406,60 @@
   </si>
   <si>
     <t>12d</t>
+  </si>
+  <si>
+    <t>6/2*</t>
+  </si>
+  <si>
+    <t>14.3</t>
+  </si>
+  <si>
+    <t>16.9</t>
+  </si>
+  <si>
+    <t>20.8</t>
+  </si>
+  <si>
+    <t>31.2</t>
+  </si>
+  <si>
+    <t>41.6</t>
+  </si>
+  <si>
+    <t>58.5</t>
+  </si>
+  <si>
+    <t>80.6</t>
+  </si>
+  <si>
+    <t>101.4</t>
+  </si>
+  <si>
+    <t>1d 18h</t>
+  </si>
+  <si>
+    <t>109.2</t>
+  </si>
+  <si>
+    <t>123.5</t>
+  </si>
+  <si>
+    <t>132.6</t>
+  </si>
+  <si>
+    <t>4d 12h</t>
+  </si>
+  <si>
+    <t>5d 12h</t>
+  </si>
+  <si>
+    <t>1.3s</t>
+  </si>
+  <si>
+    <t>Splash - 1 tile</t>
+  </si>
+  <si>
+    <t>Ground &amp; Air</t>
   </si>
 </sst>
 </file>
@@ -1225,7 +1283,7 @@
         <xdr:cNvPr id="2" name="AutoShape 1" descr="Size">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB199BBF-B873-484A-BC8D-EA3C3125F021}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1C3D133-8EE8-4E23-ABBD-318B25BCF438}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1273,17 +1331,17 @@
         <xdr:cNvPr id="3" name="AutoShape 3" descr="Damage">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D139D960-FB2C-4F91-B89D-E5C0B60372BF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1356360" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1629852-5C9D-4499-A777-812695D13E75}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1767840" y="1287780"/>
           <a:ext cx="266700" cy="259080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1321,17 +1379,17 @@
         <xdr:cNvPr id="4" name="AutoShape 4" descr="Damage">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B27A4B97-D838-47DB-BA26-EC74AAB73BD3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1965960" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C9D6E79-00DB-4DC1-B429-4D75E7A49221}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2377440" y="1287780"/>
           <a:ext cx="266700" cy="259080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1369,17 +1427,17 @@
         <xdr:cNvPr id="5" name="AutoShape 5" descr="Hitpoints">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32345089-3584-454E-8BE8-052DA9EECA73}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2552700" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{442DA563-178D-4E7F-8ADB-17BCADD1F1CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2987040" y="1287780"/>
           <a:ext cx="190500" cy="175260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1418,17 +1476,17 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31C77F8C-578E-4489-B5E8-0CCE7694A813}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3611880" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13828057-4787-4CF1-90A9-7DD61D439351}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3596640" y="1287780"/>
           <a:ext cx="190500" cy="190500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1466,17 +1524,17 @@
         <xdr:cNvPr id="7" name="AutoShape 7" descr="Time">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE188228-C1C1-4296-A06D-E6ACFF6E8A75}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4305300" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24F9BEBE-FEEB-48BB-AEA7-1B476AAE0792}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4206240" y="1287780"/>
           <a:ext cx="175260" cy="198120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1515,17 +1573,17 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAE14E2E-CB9C-4958-B08E-337346EB71FC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5364480" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{988CD871-E376-4624-86C8-49757F5CF002}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4815840" y="1287780"/>
           <a:ext cx="213360" cy="220980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1564,17 +1622,17 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD6E4FC9-C9CC-4EED-A271-750B50B4BA4C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5974080" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B45194F9-AA9F-4460-BF13-E5F9AB05C779}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5425440" y="1287780"/>
           <a:ext cx="251460" cy="251460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1612,7 +1670,7 @@
         <xdr:cNvPr id="10" name="AutoShape 10" descr="Level">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39571FD4-36F3-49D2-A22C-E974CCC0CD90}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C864962F-B7E1-4DFC-8547-9EAE2C8D78A5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1660,17 +1718,17 @@
         <xdr:cNvPr id="11" name="AutoShape 11" descr="Damage">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67783437-2BB3-4B96-91A3-F1BE31000630}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1356360" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D832D97-5EF9-4166-9C92-58B3A810295F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1767840" y="1287780"/>
           <a:ext cx="266700" cy="259080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1708,17 +1766,17 @@
         <xdr:cNvPr id="12" name="AutoShape 12" descr="Damage">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D702565C-3A1D-480E-A7BA-0082DAB94811}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1965960" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{463ACA97-125C-4496-9B7E-B49856A027AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2377440" y="1287780"/>
           <a:ext cx="266700" cy="259080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1756,17 +1814,17 @@
         <xdr:cNvPr id="13" name="AutoShape 13" descr="Hitpoints">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD918FD4-EB03-4F6C-B3EE-B2B06A22745E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2552700" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D91AD2E3-1C57-41F7-9B71-EA2727FA8A1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2987040" y="1287780"/>
           <a:ext cx="190500" cy="175260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1805,17 +1863,17 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F925A87-2AB6-479F-B93B-33A19CA97A48}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3611880" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFEF8E86-9B1A-4734-9E1A-3E016F4FBF08}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3596640" y="1287780"/>
           <a:ext cx="190500" cy="190500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1853,17 +1911,17 @@
         <xdr:cNvPr id="15" name="AutoShape 15" descr="Time">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D62622A-F0A3-4621-B726-11850B5C0478}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4305300" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{315CD2F3-B29C-46EF-BE9E-A53457272F81}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4206240" y="1287780"/>
           <a:ext cx="175260" cy="198120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1902,17 +1960,17 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A30E40F-DF12-45C2-B374-FFC5271A0222}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5364480" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{865E127F-1824-4C37-B715-20993F0A1535}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4815840" y="1287780"/>
           <a:ext cx="213360" cy="220980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1951,17 +2009,17 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30AE22C6-B11E-4281-A42C-60D1E251D8E6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5974080" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97A0F912-1903-4F5A-A090-F09C23F7DCDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5425440" y="1287780"/>
           <a:ext cx="251460" cy="251460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1999,17 +2057,17 @@
         <xdr:cNvPr id="18" name="AutoShape 18" descr="Range">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{541DBF95-AB48-481D-AB56-9946B05C87CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="8526780" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE3CEB21-705B-4BCB-9AFF-E7E23D29B5FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7254240" y="1287780"/>
           <a:ext cx="228600" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2047,17 +2105,17 @@
         <xdr:cNvPr id="19" name="AutoShape 19" descr="Attack Speed">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74DA04C1-F46A-48C2-A4EA-F57A66946241}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9136380" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A96DBCEB-1A15-492D-AAD5-F6F14408913C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7863840" y="1287780"/>
           <a:ext cx="213360" cy="251460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2095,17 +2153,17 @@
         <xdr:cNvPr id="20" name="AutoShape 20" descr="Damage Type">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{544EECDF-1F7C-4688-8D07-1E263A920933}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9745980" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B354E68E-F16F-42E7-9BF0-9EA0A4740AF2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8473440" y="1287780"/>
           <a:ext cx="289560" cy="213360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2143,17 +2201,17 @@
         <xdr:cNvPr id="21" name="AutoShape 21" descr="Favorite Target">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD773BB4-A2EC-4CF3-8A5C-9A88DA7CD7AA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10355580" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E42B403-C49B-4E3E-B9C6-A568A146A760}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9083040" y="1287780"/>
           <a:ext cx="213360" cy="182880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2186,17 +2244,17 @@
         <xdr:cNvPr id="22" name="AutoShape 1" descr="Size">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D06613C-190E-4BD8-B35B-D1B181959F9F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="7467600" y="1287780"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E9B7998-DC33-40B9-BBC3-763F58D3C764}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6035040" y="1287780"/>
           <a:ext cx="190500" cy="144780"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2216,6 +2274,54 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="AutoShape 18" descr="Range">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C2C3267-2617-47D5-A24F-EE752F815F91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7254240" y="1287780"/>
+          <a:ext cx="228600" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -2231,6 +2337,1358 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
+        <xdr:cNvPr id="7169" name="AutoShape 1" descr="Level">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B6BE9EA-F51D-333C-C35B-D4D7FAB113D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="975360" y="937260"/>
+          <a:ext cx="160020" cy="175260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7170" name="AutoShape 2" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE234EB6-7A3C-5DFD-C385-0F97AA0337C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1767840" y="937260"/>
+          <a:ext cx="266700" cy="259080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7171" name="AutoShape 3" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4866C42D-ADE0-2135-D58B-49208E8271DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2377440" y="937260"/>
+          <a:ext cx="266700" cy="259080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7172" name="AutoShape 4" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71C522E7-599C-3F9E-F33F-F45D4731847A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2987040" y="937260"/>
+          <a:ext cx="190500" cy="175260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7173" name="AutoShape 5" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68011935-2F4B-BC39-BF31-AEA81BF5C338}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3596640" y="937260"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7174" name="AutoShape 6" descr="Time">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B8BB51B-882D-4E02-B1D5-353B76227746}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4206240" y="937260"/>
+          <a:ext cx="175260" cy="198120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>220980</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7175" name="AutoShape 7" descr="Experience">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1615056C-6A23-8A9E-F8F3-CFE80DC22D30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4815840" y="937260"/>
+          <a:ext cx="213360" cy="220980"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1" descr="Size">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB199BBF-B873-484A-BC8D-EA3C3125F021}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="975360" y="365760"/>
+          <a:ext cx="190500" cy="144780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 3" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D139D960-FB2C-4F91-B89D-E5C0B60372BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1356360" y="1287780"/>
+          <a:ext cx="266700" cy="259080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 4" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B27A4B97-D838-47DB-BA26-EC74AAB73BD3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1965960" y="1287780"/>
+          <a:ext cx="266700" cy="259080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 5" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32345089-3584-454E-8BE8-052DA9EECA73}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2552700" y="1287780"/>
+          <a:ext cx="190500" cy="175260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 6" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31C77F8C-578E-4489-B5E8-0CCE7694A813}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3611880" y="1287780"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 7" descr="Time">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE188228-C1C1-4296-A06D-E6ACFF6E8A75}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4305300" y="1287780"/>
+          <a:ext cx="175260" cy="198120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>220980</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="AutoShape 8" descr="Experience">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAE14E2E-CB9C-4958-B08E-337346EB71FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5364480" y="1287780"/>
+          <a:ext cx="213360" cy="220980"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>251460</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="AutoShape 9" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD6E4FC9-C9CC-4EED-A271-750B50B4BA4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5974080" y="1287780"/>
+          <a:ext cx="251460" cy="251460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="AutoShape 10" descr="Level">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39571FD4-36F3-49D2-A22C-E974CCC0CD90}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="975360" y="1287780"/>
+          <a:ext cx="160020" cy="175260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="AutoShape 11" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67783437-2BB3-4B96-91A3-F1BE31000630}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1356360" y="1287780"/>
+          <a:ext cx="266700" cy="259080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="AutoShape 12" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D702565C-3A1D-480E-A7BA-0082DAB94811}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1965960" y="1287780"/>
+          <a:ext cx="266700" cy="259080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="AutoShape 13" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD918FD4-EB03-4F6C-B3EE-B2B06A22745E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2552700" y="1287780"/>
+          <a:ext cx="190500" cy="175260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="AutoShape 14" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F925A87-2AB6-479F-B93B-33A19CA97A48}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3611880" y="1287780"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="AutoShape 15" descr="Time">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D62622A-F0A3-4621-B726-11850B5C0478}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4305300" y="1287780"/>
+          <a:ext cx="175260" cy="198120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>220980</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="AutoShape 16" descr="Experience">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A30E40F-DF12-45C2-B374-FFC5271A0222}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5364480" y="1287780"/>
+          <a:ext cx="213360" cy="220980"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>251460</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="AutoShape 17" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30AE22C6-B11E-4281-A42C-60D1E251D8E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5974080" y="1287780"/>
+          <a:ext cx="251460" cy="251460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="AutoShape 18" descr="Range">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{541DBF95-AB48-481D-AB56-9946B05C87CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8526780" y="1287780"/>
+          <a:ext cx="228600" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>251460</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="AutoShape 19" descr="Attack Speed">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74DA04C1-F46A-48C2-A4EA-F57A66946241}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9136380" y="1287780"/>
+          <a:ext cx="213360" cy="251460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="AutoShape 20" descr="Damage Type">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{544EECDF-1F7C-4688-8D07-1E263A920933}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9745980" y="1287780"/>
+          <a:ext cx="289560" cy="213360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="AutoShape 21" descr="Favorite Target">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD773BB4-A2EC-4CF3-8A5C-9A88DA7CD7AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10355580" y="1287780"/>
+          <a:ext cx="213360" cy="182880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="190500" cy="144780"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="AutoShape 1" descr="Size">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D06613C-190E-4BD8-B35B-D1B181959F9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7467600" y="1287780"/>
+          <a:ext cx="190500" cy="144780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
         <xdr:cNvPr id="23" name="AutoShape 9" descr="Level">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
@@ -4295,1888 +5753,6 @@
         <a:xfrm>
           <a:off x="15218229" y="3407229"/>
           <a:ext cx="213360" cy="226422"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 1" descr="Size">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCFBE453-5FFF-49E9-B0B1-AA447DD5BD3A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="975360" y="365760"/>
-          <a:ext cx="190500" cy="144780"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>259080</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 3" descr="Damage">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1FEFE79-4EA4-4112-A3E4-1184D04845EF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1767840" y="1287780"/>
-          <a:ext cx="266700" cy="259080"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>259080</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="AutoShape 4" descr="Damage">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BE0CFCE-C41B-46C6-B833-2DB7437D1193}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2377440" y="1287780"/>
-          <a:ext cx="266700" cy="259080"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="AutoShape 5" descr="Hitpoints">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F64E606E-2D23-48E4-B69D-2F8C4E3C97E9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2987040" y="1287780"/>
-          <a:ext cx="190500" cy="175260"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="AutoShape 6" descr="Gold">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4235908B-A1CC-4C13-A94B-B1210445B244}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3596640" y="1287780"/>
-          <a:ext cx="190500" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>175260</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>198120</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="AutoShape 7" descr="Time">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D44EBE0-ACD3-42DA-99E1-8440AFC56339}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4290060" y="1287780"/>
-          <a:ext cx="175260" cy="198120"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>213360</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>220980</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="AutoShape 8" descr="Experience">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B2F292B-49E3-49EC-B9FA-EE16A8367594}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4899660" y="1287780"/>
-          <a:ext cx="213360" cy="220980"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>251460</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>251460</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="AutoShape 9" descr="Town Hall">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17CE37BB-14DA-41D7-9077-354D69921F4E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5509260" y="1287780"/>
-          <a:ext cx="251460" cy="251460"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="AutoShape 10" descr="Level">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B175A910-43B8-43C1-AD81-0420C3788781}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="975360" y="1287780"/>
-          <a:ext cx="160020" cy="175260"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>259080</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="AutoShape 11" descr="Damage">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{934C1CE9-76A1-40E0-B447-3B1EF7CD76ED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1767840" y="1287780"/>
-          <a:ext cx="266700" cy="259080"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>259080</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="AutoShape 12" descr="Damage">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AFF534C-9363-4242-9728-4DF4DE6C8177}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2377440" y="1287780"/>
-          <a:ext cx="266700" cy="259080"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="AutoShape 13" descr="Hitpoints">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DD4C963-53D6-4A63-9B9C-7A607CED799C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2987040" y="1287780"/>
-          <a:ext cx="190500" cy="175260"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="AutoShape 14" descr="Gold">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8CF4A32-9B98-49CC-B8A2-3C0A9EA23849}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3596640" y="1287780"/>
-          <a:ext cx="190500" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>175260</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>198120</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="AutoShape 15" descr="Time">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F15AF1A-6E08-469F-8B5E-C3DACBAEA8CB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4290060" y="1287780"/>
-          <a:ext cx="175260" cy="198120"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>213360</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>220980</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="AutoShape 16" descr="Experience">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8FC6ABB-9906-460C-AC5D-13E894C08BC3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4899660" y="1287780"/>
-          <a:ext cx="213360" cy="220980"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>251460</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>251460</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="AutoShape 17" descr="Town Hall">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64AC3501-D175-4D95-9962-E5731DF4FA2A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5509260" y="1287780"/>
-          <a:ext cx="251460" cy="251460"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="AutoShape 18" descr="Range">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D94DFD3B-A3D3-4196-B2C0-FCEAC5AFEC35}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="7338060" y="1287780"/>
-          <a:ext cx="228600" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>213360</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>251460</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="AutoShape 19" descr="Attack Speed">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1202C5DA-D637-4F29-8A81-3E96A649C811}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="7947660" y="1287780"/>
-          <a:ext cx="213360" cy="251460"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>289560</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>213360</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="AutoShape 20" descr="Damage Type">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89502CF8-4445-45F7-99FD-BEB4D0B95308}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="8557260" y="1287780"/>
-          <a:ext cx="289560" cy="213360"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>213360</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>182880</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="AutoShape 21" descr="Favorite Target">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B35F65A-CC39-4167-B26B-C42918840A5B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9166860" y="1287780"/>
-          <a:ext cx="213360" cy="182880"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="190500" cy="144780"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="AutoShape 1" descr="Size">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0484BB9-4873-4F12-89C0-6674BADE71D0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6118860" y="1287780"/>
-          <a:ext cx="190500" cy="144780"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5129" name="AutoShape 9" descr="Level">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F95DF4B-B8B8-0736-3D5C-73B27185F169}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="975360" y="937260"/>
-          <a:ext cx="160020" cy="175260"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5130" name="AutoShape 10" descr="Hitpoints">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BBF3725-7C86-6F05-0E2F-C8C86D62426D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1767840" y="937260"/>
-          <a:ext cx="190500" cy="175260"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5131" name="AutoShape 11" descr="Gold">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FDB31DD-2BB3-4AEB-A0DA-958362C6303A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2377440" y="937260"/>
-          <a:ext cx="190500" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5132" name="AutoShape 12" descr="Gold">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8711663-0E60-9DDF-4FB8-7E28468905E8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2987040" y="937260"/>
-          <a:ext cx="190500" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>175260</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5133" name="AutoShape 13" descr="Elixir">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4" tooltip="Elixir"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFDCE10C-B065-4408-3F22-1DB175FC7CC0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3596640" y="937260"/>
-          <a:ext cx="175260" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>175260</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5134" name="AutoShape 14" descr="Elixir">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4" tooltip="Elixir"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B61DF097-3C9E-F324-0400-E9E621FEA32E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4290060" y="937260"/>
-          <a:ext cx="175260" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>251460</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>220980</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5135" name="AutoShape 15" descr="Magic Items">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5" tooltip="Magic Items"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35DFD8FF-EC5C-1805-C0D9-595FF19E1DE6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4899660" y="937260"/>
-          <a:ext cx="251460" cy="220980"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>251460</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>251460</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5136" name="AutoShape 16" descr="Town Hall">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAEA1871-FA25-F01A-D9D1-B8481E6E8839}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5509260" y="937260"/>
-          <a:ext cx="251460" cy="251460"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5137" name="AutoShape 17" descr="Level">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27324C3B-6A3A-B010-3D20-2B1FA8E88DEF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="24970740" y="3192780"/>
-          <a:ext cx="160020" cy="175260"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>41</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>41</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5138" name="AutoShape 18" descr="Hitpoints">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A679ED43-3D09-9A43-20D2-894E28879BC3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="25580340" y="3192780"/>
-          <a:ext cx="190500" cy="175260"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5139" name="AutoShape 19" descr="Gold">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EE19A3E-5172-1A3F-6E07-172296387110}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="26189940" y="3192780"/>
-          <a:ext cx="190500" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5140" name="AutoShape 20" descr="Gold">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F5C169F-618E-EC5E-7A75-C7B1DBE414E9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="26799540" y="3192780"/>
-          <a:ext cx="190500" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>175260</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5141" name="AutoShape 21" descr="Elixir">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4" tooltip="Elixir"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A037060A-A3C1-91E3-CB79-19275B2FE581}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="27409140" y="3192780"/>
-          <a:ext cx="175260" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>175260</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5142" name="AutoShape 22" descr="Elixir">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4" tooltip="Elixir"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CA8969C-2303-65A8-BA5F-2AF562FEE790}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="28018740" y="3192780"/>
-          <a:ext cx="175260" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>251460</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5143" name="AutoShape 23" descr="Magic Items">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B72EDE8C-6A5B-530C-6B47-D0D39CF4121E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="28628340" y="3192780"/>
-          <a:ext cx="251460" cy="220980"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>251460</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5144" name="AutoShape 24" descr="Town Hall">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89DC6CE5-3813-E83F-ED00-96EE34CFE5D6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="29237940" y="3192780"/>
-          <a:ext cx="251460" cy="251460"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="251460" cy="220980"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="AutoShape 23" descr="Magic Items">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA183CEA-5C64-4F45-B891-04AF6D7156C2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="26189940" y="3192780"/>
-          <a:ext cx="251460" cy="220980"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="251460" cy="251460"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="AutoShape 24" descr="Town Hall">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5623036D-4B12-460A-A511-99F76EF0045A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="26189940" y="3192780"/>
-          <a:ext cx="251460" cy="251460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6218,17 +5794,17 @@
         <xdr:cNvPr id="2" name="AutoShape 1" descr="Size">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0674C7B-BF8E-4DA8-94C6-9BBE7010DEFD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="975360" y="716280"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCFBE453-5FFF-49E9-B0B1-AA447DD5BD3A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="975360" y="365760"/>
           <a:ext cx="190500" cy="144780"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6266,17 +5842,17 @@
         <xdr:cNvPr id="3" name="AutoShape 3" descr="Damage">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{736D4203-89DD-42F5-9153-EA5BD045B87F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1767840" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1FEFE79-4EA4-4112-A3E4-1184D04845EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1767840" y="1287780"/>
           <a:ext cx="266700" cy="259080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6314,17 +5890,17 @@
         <xdr:cNvPr id="4" name="AutoShape 4" descr="Damage">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD22D101-F2CD-4E2F-B4DB-F1689615CA86}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2377440" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BE0CFCE-C41B-46C6-B833-2DB7437D1193}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2377440" y="1287780"/>
           <a:ext cx="266700" cy="259080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6362,17 +5938,17 @@
         <xdr:cNvPr id="5" name="AutoShape 5" descr="Hitpoints">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CDC99C6-C3A8-4832-A58C-614E3E7E47AF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2987040" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F64E606E-2D23-48E4-B69D-2F8C4E3C97E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2987040" y="1287780"/>
           <a:ext cx="190500" cy="175260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6411,17 +5987,17 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9732B9C-6C19-4222-A80E-073FAAADD5B3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3596640" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4235908B-A1CC-4C13-A94B-B1210445B244}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3596640" y="1287780"/>
           <a:ext cx="190500" cy="190500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6459,17 +6035,17 @@
         <xdr:cNvPr id="7" name="AutoShape 7" descr="Time">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A465409-CFBB-4179-BC22-CD446B3AB9E0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4206240" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D44EBE0-ACD3-42DA-99E1-8440AFC56339}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4290060" y="1287780"/>
           <a:ext cx="175260" cy="198120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6508,17 +6084,17 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E47A264-350E-423D-84A5-9148E4A88B36}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4815840" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B2F292B-49E3-49EC-B9FA-EE16A8367594}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4899660" y="1287780"/>
           <a:ext cx="213360" cy="220980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6557,17 +6133,17 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D58E467-1524-4FB3-891D-7191A9401F7D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5425440" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17CE37BB-14DA-41D7-9077-354D69921F4E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5509260" y="1287780"/>
           <a:ext cx="251460" cy="251460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6605,17 +6181,17 @@
         <xdr:cNvPr id="10" name="AutoShape 10" descr="Level">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE247D23-A563-4EFB-A77F-B03B79A262E0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="975360" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B175A910-43B8-43C1-AD81-0420C3788781}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="975360" y="1287780"/>
           <a:ext cx="160020" cy="175260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6653,17 +6229,17 @@
         <xdr:cNvPr id="11" name="AutoShape 11" descr="Damage">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F577168-229F-4C2E-B71B-96EB81EB833E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1767840" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{934C1CE9-76A1-40E0-B447-3B1EF7CD76ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1767840" y="1287780"/>
           <a:ext cx="266700" cy="259080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6701,17 +6277,17 @@
         <xdr:cNvPr id="12" name="AutoShape 12" descr="Damage">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46C424EE-46AA-4EBF-B856-C2AFD1A06C9E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2377440" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AFF534C-9363-4242-9728-4DF4DE6C8177}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2377440" y="1287780"/>
           <a:ext cx="266700" cy="259080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6749,17 +6325,17 @@
         <xdr:cNvPr id="13" name="AutoShape 13" descr="Hitpoints">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE1CCB4F-2719-430F-920D-216296F81DC6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2987040" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DD4C963-53D6-4A63-9B9C-7A607CED799C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2987040" y="1287780"/>
           <a:ext cx="190500" cy="175260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6798,17 +6374,17 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9989FFE-E496-4230-861B-9DBB22C8DEA6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3596640" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8CF4A32-9B98-49CC-B8A2-3C0A9EA23849}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3596640" y="1287780"/>
           <a:ext cx="190500" cy="190500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6846,17 +6422,17 @@
         <xdr:cNvPr id="15" name="AutoShape 15" descr="Time">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31A05486-D55F-48C1-B0C7-2C7E38887D7B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4206240" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F15AF1A-6E08-469F-8B5E-C3DACBAEA8CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4290060" y="1287780"/>
           <a:ext cx="175260" cy="198120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6895,17 +6471,17 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04EBB3AB-286E-490D-B600-2947D1D15BE3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4815840" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8FC6ABB-9906-460C-AC5D-13E894C08BC3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4899660" y="1287780"/>
           <a:ext cx="213360" cy="220980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6944,17 +6520,17 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF7B9FFB-9951-48C7-A17C-B6ACBF714ECA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5425440" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64AC3501-D175-4D95-9962-E5731DF4FA2A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5509260" y="1287780"/>
           <a:ext cx="251460" cy="251460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6992,17 +6568,17 @@
         <xdr:cNvPr id="18" name="AutoShape 18" descr="Range">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1F86F31-1F62-4CD0-9BBA-6077ACF881DE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6644640" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D94DFD3B-A3D3-4196-B2C0-FCEAC5AFEC35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7338060" y="1287780"/>
           <a:ext cx="228600" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7040,17 +6616,17 @@
         <xdr:cNvPr id="19" name="AutoShape 19" descr="Attack Speed">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0524D65-A020-4383-87DE-81C6FB02D86C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="7254240" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1202C5DA-D637-4F29-8A81-3E96A649C811}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7947660" y="1287780"/>
           <a:ext cx="213360" cy="251460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7088,17 +6664,17 @@
         <xdr:cNvPr id="20" name="AutoShape 20" descr="Damage Type">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{422203FD-CA08-4590-9E15-E86823B9F8FB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="7863840" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89502CF8-4445-45F7-99FD-BEB4D0B95308}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8557260" y="1287780"/>
           <a:ext cx="289560" cy="213360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7136,17 +6712,17 @@
         <xdr:cNvPr id="21" name="AutoShape 21" descr="Favorite Target">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5745F97-D99A-4DAE-A0E6-E6F54B54C1EE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="8473440" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B35F65A-CC39-4167-B26B-C42918840A5B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9166860" y="1287780"/>
           <a:ext cx="213360" cy="182880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7179,18 +6755,886 @@
         <xdr:cNvPr id="22" name="AutoShape 1" descr="Size">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E7E888B-53E6-4004-8350-8A658D362ACB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6035040" y="1638300"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0484BB9-4873-4F12-89C0-6674BADE71D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6118860" y="1287780"/>
           <a:ext cx="190500" cy="144780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5129" name="AutoShape 9" descr="Level">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F95DF4B-B8B8-0736-3D5C-73B27185F169}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="975360" y="937260"/>
+          <a:ext cx="160020" cy="175260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5130" name="AutoShape 10" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BBF3725-7C86-6F05-0E2F-C8C86D62426D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1767840" y="937260"/>
+          <a:ext cx="190500" cy="175260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5131" name="AutoShape 11" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FDB31DD-2BB3-4AEB-A0DA-958362C6303A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2377440" y="937260"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5132" name="AutoShape 12" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8711663-0E60-9DDF-4FB8-7E28468905E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2987040" y="937260"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5133" name="AutoShape 13" descr="Elixir">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4" tooltip="Elixir"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFDCE10C-B065-4408-3F22-1DB175FC7CC0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3596640" y="937260"/>
+          <a:ext cx="175260" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5134" name="AutoShape 14" descr="Elixir">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4" tooltip="Elixir"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B61DF097-3C9E-F324-0400-E9E621FEA32E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4290060" y="937260"/>
+          <a:ext cx="175260" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>220980</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5135" name="AutoShape 15" descr="Magic Items">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5" tooltip="Magic Items"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35DFD8FF-EC5C-1805-C0D9-595FF19E1DE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4899660" y="937260"/>
+          <a:ext cx="251460" cy="220980"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>251460</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5136" name="AutoShape 16" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAEA1871-FA25-F01A-D9D1-B8481E6E8839}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5509260" y="937260"/>
+          <a:ext cx="251460" cy="251460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5137" name="AutoShape 17" descr="Level">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27324C3B-6A3A-B010-3D20-2B1FA8E88DEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="24970740" y="3192780"/>
+          <a:ext cx="160020" cy="175260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5138" name="AutoShape 18" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A679ED43-3D09-9A43-20D2-894E28879BC3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="25580340" y="3192780"/>
+          <a:ext cx="190500" cy="175260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5139" name="AutoShape 19" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EE19A3E-5172-1A3F-6E07-172296387110}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="26189940" y="3192780"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5140" name="AutoShape 20" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F5C169F-618E-EC5E-7A75-C7B1DBE414E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="26799540" y="3192780"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5141" name="AutoShape 21" descr="Elixir">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4" tooltip="Elixir"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A037060A-A3C1-91E3-CB79-19275B2FE581}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="27409140" y="3192780"/>
+          <a:ext cx="175260" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5142" name="AutoShape 22" descr="Elixir">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4" tooltip="Elixir"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CA8969C-2303-65A8-BA5F-2AF562FEE790}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="28018740" y="3192780"/>
+          <a:ext cx="175260" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5143" name="AutoShape 23" descr="Magic Items">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B72EDE8C-6A5B-530C-6B47-D0D39CF4121E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="28628340" y="3192780"/>
+          <a:ext cx="251460" cy="220980"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5144" name="AutoShape 24" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89DC6CE5-3813-E83F-ED00-96EE34CFE5D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="29237940" y="3192780"/>
+          <a:ext cx="251460" cy="251460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="251460" cy="220980"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="AutoShape 23" descr="Magic Items">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA183CEA-5C64-4F45-B891-04AF6D7156C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="26189940" y="3192780"/>
+          <a:ext cx="251460" cy="220980"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="251460" cy="251460"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="AutoShape 24" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5623036D-4B12-460A-A511-99F76EF0045A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="26189940" y="3192780"/>
+          <a:ext cx="251460" cy="251460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7232,6 +7676,1020 @@
         <xdr:cNvPr id="2" name="AutoShape 1" descr="Size">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0674C7B-BF8E-4DA8-94C6-9BBE7010DEFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="975360" y="716280"/>
+          <a:ext cx="190500" cy="144780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 3" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{736D4203-89DD-42F5-9153-EA5BD045B87F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1767840" y="1638300"/>
+          <a:ext cx="266700" cy="259080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 4" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD22D101-F2CD-4E2F-B4DB-F1689615CA86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2377440" y="1638300"/>
+          <a:ext cx="266700" cy="259080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 5" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CDC99C6-C3A8-4832-A58C-614E3E7E47AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2987040" y="1638300"/>
+          <a:ext cx="190500" cy="175260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 6" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9732B9C-6C19-4222-A80E-073FAAADD5B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3596640" y="1638300"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 7" descr="Time">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A465409-CFBB-4179-BC22-CD446B3AB9E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4206240" y="1638300"/>
+          <a:ext cx="175260" cy="198120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>220980</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="AutoShape 8" descr="Experience">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E47A264-350E-423D-84A5-9148E4A88B36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4815840" y="1638300"/>
+          <a:ext cx="213360" cy="220980"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>251460</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="AutoShape 9" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D58E467-1524-4FB3-891D-7191A9401F7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5425440" y="1638300"/>
+          <a:ext cx="251460" cy="251460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="AutoShape 10" descr="Level">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE247D23-A563-4EFB-A77F-B03B79A262E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="975360" y="1638300"/>
+          <a:ext cx="160020" cy="175260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="AutoShape 11" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F577168-229F-4C2E-B71B-96EB81EB833E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1767840" y="1638300"/>
+          <a:ext cx="266700" cy="259080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="AutoShape 12" descr="Damage">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46C424EE-46AA-4EBF-B856-C2AFD1A06C9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2377440" y="1638300"/>
+          <a:ext cx="266700" cy="259080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="AutoShape 13" descr="Hitpoints">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE1CCB4F-2719-430F-920D-216296F81DC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2987040" y="1638300"/>
+          <a:ext cx="190500" cy="175260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="AutoShape 14" descr="Gold">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Gold"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9989FFE-E496-4230-861B-9DBB22C8DEA6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3596640" y="1638300"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="AutoShape 15" descr="Time">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31A05486-D55F-48C1-B0C7-2C7E38887D7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4206240" y="1638300"/>
+          <a:ext cx="175260" cy="198120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>220980</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="AutoShape 16" descr="Experience">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Experience"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04EBB3AB-286E-490D-B600-2947D1D15BE3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4815840" y="1638300"/>
+          <a:ext cx="213360" cy="220980"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>251460</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="AutoShape 17" descr="Town Hall">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3" tooltip="Town Hall"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF7B9FFB-9951-48C7-A17C-B6ACBF714ECA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5425440" y="1638300"/>
+          <a:ext cx="251460" cy="251460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="AutoShape 18" descr="Range">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1F86F31-1F62-4CD0-9BBA-6077ACF881DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6644640" y="1638300"/>
+          <a:ext cx="228600" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>251460</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="AutoShape 19" descr="Attack Speed">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0524D65-A020-4383-87DE-81C6FB02D86C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7254240" y="1638300"/>
+          <a:ext cx="213360" cy="251460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="AutoShape 20" descr="Damage Type">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{422203FD-CA08-4590-9E15-E86823B9F8FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7863840" y="1638300"/>
+          <a:ext cx="289560" cy="213360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="AutoShape 21" descr="Favorite Target">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5745F97-D99A-4DAE-A0E6-E6F54B54C1EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8473440" y="1638300"/>
+          <a:ext cx="213360" cy="182880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="190500" cy="144780"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="AutoShape 1" descr="Size">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E7E888B-53E6-4004-8350-8A658D362ACB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6035040" y="1638300"/>
+          <a:ext cx="190500" cy="144780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1" descr="Size">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA2618C2-D7A9-4BBC-B830-4E6B25630AC7}"/>
             </a:ext>
           </a:extLst>
@@ -8322,7 +9780,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -9680,6 +11138,1245 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F055A77-4ADA-4D87-ADBA-9E92B9CBE2DF}">
+  <dimension ref="A3:AL24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="31"/>
+    </row>
+    <row r="7" spans="1:38" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="L7" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="N7" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="O7" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="P7" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2">
+        <v>2</v>
+      </c>
+      <c r="W7" s="2">
+        <v>3</v>
+      </c>
+      <c r="X7" s="2">
+        <v>4</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>5</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>6</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>7</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>8</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>9</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>10</v>
+      </c>
+      <c r="AE7" s="2">
+        <v>11</v>
+      </c>
+      <c r="AF7" s="2">
+        <v>12</v>
+      </c>
+      <c r="AG7" s="2">
+        <v>13</v>
+      </c>
+      <c r="AH7" s="2">
+        <v>14</v>
+      </c>
+      <c r="AI7" s="2">
+        <v>15</v>
+      </c>
+      <c r="AJ7" s="2">
+        <v>16</v>
+      </c>
+      <c r="AK7" s="2">
+        <v>17</v>
+      </c>
+      <c r="AL7" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8">
+        <v>11</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="8">
+        <v>620</v>
+      </c>
+      <c r="H8" s="27">
+        <v>100000</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="8">
+        <v>60</v>
+      </c>
+      <c r="K8" s="8">
+        <v>5</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="8">
+        <v>7</v>
+      </c>
+      <c r="N8" s="8">
+        <v>7</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R8">
+        <f>INDEX($U$8:$AL$8,MATCH(K8,$U$7:$AL$7,0))</f>
+        <v>1</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
+      <c r="X8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>2</v>
+      </c>
+      <c r="AA8" s="5">
+        <v>2</v>
+      </c>
+      <c r="AB8" s="4">
+        <v>3</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="5">
+        <v>4</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>5</v>
+      </c>
+      <c r="AF8" s="5">
+        <v>5</v>
+      </c>
+      <c r="AG8" s="5">
+        <v>5</v>
+      </c>
+      <c r="AH8" s="5">
+        <v>5</v>
+      </c>
+      <c r="AI8" s="5">
+        <v>5</v>
+      </c>
+      <c r="AJ8" s="5">
+        <v>5</v>
+      </c>
+      <c r="AK8" s="5">
+        <v>5</v>
+      </c>
+      <c r="AL8" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="8">
+        <v>2</v>
+      </c>
+      <c r="E9" s="8">
+        <v>13</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" s="8">
+        <v>650</v>
+      </c>
+      <c r="H9" s="27">
+        <v>150000</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="8">
+        <v>73</v>
+      </c>
+      <c r="K9" s="8">
+        <v>5</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="8">
+        <v>7</v>
+      </c>
+      <c r="N9" s="8">
+        <v>7</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R9">
+        <f>INDEX($U$8:$AL$8,MATCH(K9,$U$7:$AL$7,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="8">
+        <v>3</v>
+      </c>
+      <c r="E10" s="8">
+        <v>16</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="G10" s="8">
+        <v>680</v>
+      </c>
+      <c r="H10" s="27">
+        <v>250000</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="8">
+        <v>120</v>
+      </c>
+      <c r="K10" s="10">
+        <v>6</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="8">
+        <v>7</v>
+      </c>
+      <c r="N10" s="8">
+        <v>7</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R10">
+        <f>INDEX($U$8:$AL$8,MATCH(K10,$U$7:$AL$7,0))</f>
+        <v>2</v>
+      </c>
+      <c r="T10" s="3"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+    </row>
+    <row r="11" spans="1:38" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="8">
+        <v>4</v>
+      </c>
+      <c r="E11" s="8">
+        <v>20</v>
+      </c>
+      <c r="F11" s="8">
+        <v>26</v>
+      </c>
+      <c r="G11" s="8">
+        <v>730</v>
+      </c>
+      <c r="H11" s="27">
+        <v>400000</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="8">
+        <v>169</v>
+      </c>
+      <c r="K11" s="8">
+        <v>7</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M11" s="8">
+        <v>7</v>
+      </c>
+      <c r="N11" s="8">
+        <v>7</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R11">
+        <f>INDEX($U$8:$AL$8,MATCH(K11,$U$7:$AL$7,0))</f>
+        <v>2</v>
+      </c>
+      <c r="T11" s="3"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+      <c r="AA11" s="5"/>
+      <c r="AB11" s="5"/>
+      <c r="AC11" s="4"/>
+    </row>
+    <row r="12" spans="1:38" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="8">
+        <v>5</v>
+      </c>
+      <c r="E12" s="8">
+        <v>24</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="8">
+        <v>840</v>
+      </c>
+      <c r="H12" s="27">
+        <v>550000</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" s="8">
+        <v>189</v>
+      </c>
+      <c r="K12" s="8">
+        <v>8</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="8">
+        <v>7</v>
+      </c>
+      <c r="N12" s="8">
+        <v>7</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R12">
+        <f>INDEX($U$8:$AL$8,MATCH(K12,$U$7:$AL$7,0))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="8">
+        <v>6</v>
+      </c>
+      <c r="E13" s="8">
+        <v>32</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="G13" s="8">
+        <v>960</v>
+      </c>
+      <c r="H13" s="27">
+        <v>660000</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" s="8">
+        <v>207</v>
+      </c>
+      <c r="K13" s="8">
+        <v>8</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M13" s="8">
+        <v>7</v>
+      </c>
+      <c r="N13" s="8">
+        <v>7</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R13">
+        <f>INDEX($U$8:$AL$8,MATCH(K13,$U$7:$AL$7,0))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="8">
+        <v>7</v>
+      </c>
+      <c r="E14" s="8">
+        <v>40</v>
+      </c>
+      <c r="F14" s="8">
+        <v>52</v>
+      </c>
+      <c r="G14" s="27">
+        <v>1200</v>
+      </c>
+      <c r="H14" s="27">
+        <v>1000000</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="J14" s="8">
+        <v>254</v>
+      </c>
+      <c r="K14" s="10">
+        <v>9</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="8">
+        <v>7</v>
+      </c>
+      <c r="N14" s="8">
+        <v>7</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R14">
+        <f>INDEX($U$8:$AL$8,MATCH(K14,$U$7:$AL$7,0))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="8">
+        <v>8</v>
+      </c>
+      <c r="E15" s="8">
+        <v>45</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G15" s="27">
+        <v>1440</v>
+      </c>
+      <c r="H15" s="27">
+        <v>1100000</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15" s="8">
+        <v>268</v>
+      </c>
+      <c r="K15" s="8">
+        <v>10</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M15" s="8">
+        <v>7</v>
+      </c>
+      <c r="N15" s="8">
+        <v>7</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R15">
+        <f>INDEX($U$8:$AL$8,MATCH(K15,$U$7:$AL$7,0))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="8">
+        <v>9</v>
+      </c>
+      <c r="E16" s="8">
+        <v>50</v>
+      </c>
+      <c r="F16" s="8">
+        <v>65</v>
+      </c>
+      <c r="G16" s="27">
+        <v>1600</v>
+      </c>
+      <c r="H16" s="27">
+        <v>1300000</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" s="8">
+        <v>293</v>
+      </c>
+      <c r="K16" s="8">
+        <v>10</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M16" s="8">
+        <v>7</v>
+      </c>
+      <c r="N16" s="8">
+        <v>7</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R16">
+        <f>INDEX($U$8:$AL$8,MATCH(K16,$U$7:$AL$7,0))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="8">
+        <v>10</v>
+      </c>
+      <c r="E17" s="8">
+        <v>62</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G17" s="27">
+        <v>1900</v>
+      </c>
+      <c r="H17" s="27">
+        <v>2000000</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="J17" s="8">
+        <v>328</v>
+      </c>
+      <c r="K17" s="10">
+        <v>11</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="8">
+        <v>7</v>
+      </c>
+      <c r="N17" s="8">
+        <v>7</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R17">
+        <f>INDEX($U$8:$AL$8,MATCH(K17,$U$7:$AL$7,0))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="8">
+        <v>11</v>
+      </c>
+      <c r="E18" s="8">
+        <v>70</v>
+      </c>
+      <c r="F18" s="8">
+        <v>91</v>
+      </c>
+      <c r="G18" s="27">
+        <v>2120</v>
+      </c>
+      <c r="H18" s="27">
+        <v>2500000</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="8">
+        <v>360</v>
+      </c>
+      <c r="K18" s="8">
+        <v>12</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="8">
+        <v>7</v>
+      </c>
+      <c r="N18" s="8">
+        <v>7</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R18">
+        <f>INDEX($U$8:$AL$8,MATCH(K18,$U$7:$AL$7,0))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="8">
+        <v>12</v>
+      </c>
+      <c r="E19" s="8">
+        <v>78</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" s="27">
+        <v>2240</v>
+      </c>
+      <c r="H19" s="27">
+        <v>2600000</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="J19" s="8">
+        <v>388</v>
+      </c>
+      <c r="K19" s="8">
+        <v>13</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M19" s="8">
+        <v>7</v>
+      </c>
+      <c r="N19" s="8">
+        <v>7</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R19">
+        <f>INDEX($U$8:$AL$8,MATCH(K19,$U$7:$AL$7,0))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="8">
+        <v>13</v>
+      </c>
+      <c r="E20" s="8">
+        <v>84</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="G20" s="27">
+        <v>2500</v>
+      </c>
+      <c r="H20" s="27">
+        <v>3000000</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J20" s="8">
+        <v>415</v>
+      </c>
+      <c r="K20" s="8">
+        <v>13</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="8">
+        <v>7</v>
+      </c>
+      <c r="N20" s="8">
+        <v>7</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q20" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R20">
+        <f>INDEX($U$8:$AL$8,MATCH(K20,$U$7:$AL$7,0))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="8">
+        <v>14</v>
+      </c>
+      <c r="E21" s="8">
+        <v>90</v>
+      </c>
+      <c r="F21" s="8">
+        <v>117</v>
+      </c>
+      <c r="G21" s="27">
+        <v>2800</v>
+      </c>
+      <c r="H21" s="27">
+        <v>4500000</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="J21" s="8">
+        <v>509</v>
+      </c>
+      <c r="K21" s="10">
+        <v>14</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="8">
+        <v>7</v>
+      </c>
+      <c r="N21" s="8">
+        <v>7</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q21" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R21">
+        <f>INDEX($U$8:$AL$8,MATCH(K21,$U$7:$AL$7,0))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="8">
+        <v>15</v>
+      </c>
+      <c r="E22" s="8">
+        <v>95</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="G22" s="27">
+        <v>3000</v>
+      </c>
+      <c r="H22" s="27">
+        <v>5500000</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="J22" s="8">
+        <v>587</v>
+      </c>
+      <c r="K22" s="8">
+        <v>15</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="8">
+        <v>7</v>
+      </c>
+      <c r="N22" s="8">
+        <v>7</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R22">
+        <f>INDEX($U$8:$AL$8,MATCH(K22,$U$7:$AL$7,0))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="8">
+        <v>16</v>
+      </c>
+      <c r="E23" s="8">
+        <v>102</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" s="27">
+        <v>3150</v>
+      </c>
+      <c r="H23" s="27">
+        <v>8000000</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="J23" s="8">
+        <v>623</v>
+      </c>
+      <c r="K23" s="8">
+        <v>16</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="8">
+        <v>7</v>
+      </c>
+      <c r="N23" s="8">
+        <v>7</v>
+      </c>
+      <c r="O23" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P23" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q23" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R23">
+        <f>INDEX($U$8:$AL$8,MATCH(K23,$U$7:$AL$7,0))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="11">
+        <v>17</v>
+      </c>
+      <c r="E24" s="11">
+        <v>110</v>
+      </c>
+      <c r="F24" s="11">
+        <v>143</v>
+      </c>
+      <c r="G24" s="28">
+        <v>3300</v>
+      </c>
+      <c r="H24" s="28">
+        <v>14000000</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="J24" s="11">
+        <v>689</v>
+      </c>
+      <c r="K24" s="11">
+        <v>17</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="8">
+        <v>7</v>
+      </c>
+      <c r="N24" s="8">
+        <v>7</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P24" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="R24">
+        <f>INDEX($U$8:$AL$8,MATCH(K24,$U$7:$AL$7,0))</f>
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="T7" r:id="rId1" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{D0A29575-C691-4C57-918F-2EFE3D1804DC}"/>
+    <hyperlink ref="J7" r:id="rId2" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{0813305B-0FD0-42AC-BFEE-162626B6ED78}"/>
+    <hyperlink ref="K7" r:id="rId3" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{1EF7BE34-26C7-4FE9-9457-47F469E48A54}"/>
+    <hyperlink ref="H5" r:id="rId4" location="Gold" tooltip="Resources" display="https://clashofclans.fandom.com/wiki/Resources - Gold" xr:uid="{039C0449-1694-4F42-AF04-02D8F3B53F2B}"/>
+    <hyperlink ref="J5" r:id="rId5" tooltip="Experience" display="https://clashofclans.fandom.com/wiki/Experience" xr:uid="{61467575-8A6E-4139-8488-40BE24D7461D}"/>
+    <hyperlink ref="K5" r:id="rId6" tooltip="Town Hall" display="https://clashofclans.fandom.com/wiki/Town_Hall" xr:uid="{78CE5D80-F3D4-4ED6-9677-D1CD0D4E3531}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId7"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD7CF795-0A07-4C9D-9E02-EA0EB50F9192}">
   <dimension ref="A3:AQ31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9849,10 +12546,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D8" s="8">
         <v>1</v>
@@ -9862,19 +12559,19 @@
         <v>400</v>
       </c>
       <c r="H8" s="36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I8" s="36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J8" s="36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K8" s="8">
         <v>1</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="30"/>
@@ -9948,10 +12645,10 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D9" s="8">
         <v>2</v>
@@ -9964,7 +12661,7 @@
         <v>1000</v>
       </c>
       <c r="I9" s="37" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J9" s="36">
         <v>3</v>
@@ -9973,7 +12670,7 @@
         <v>2</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="30"/>
@@ -9991,10 +12688,10 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D10" s="8">
         <v>3</v>
@@ -10016,7 +12713,7 @@
         <v>3</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="30"/>
@@ -10037,10 +12734,10 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D11" s="8">
         <v>4</v>
@@ -10062,7 +12759,7 @@
         <v>4</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M11" s="7"/>
       <c r="N11" s="30"/>
@@ -10074,7 +12771,7 @@
         <v>1</v>
       </c>
       <c r="U11" s="16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="V11" s="16" t="s">
         <v>9</v>
@@ -10089,10 +12786,10 @@
         <v>12</v>
       </c>
       <c r="Z11" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AA11" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AD11" s="3"/>
       <c r="AO11" s="17"/>
@@ -10104,10 +12801,10 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D12" s="8">
         <v>5</v>
@@ -10129,7 +12826,7 @@
         <v>5</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="30"/>
@@ -10146,13 +12843,13 @@
       <c r="X12" s="17"/>
       <c r="Y12" s="19"/>
       <c r="Z12" s="35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA12" s="35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AC12" s="16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AD12" s="16" t="s">
         <v>9</v>
@@ -10167,10 +12864,10 @@
         <v>12</v>
       </c>
       <c r="AH12" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AI12" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO12" s="8"/>
       <c r="AP12" s="8"/>
@@ -10181,10 +12878,10 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13" s="8">
         <v>6</v>
@@ -10206,7 +12903,7 @@
         <v>6</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M13" s="7"/>
       <c r="N13" s="30"/>
@@ -10224,19 +12921,19 @@
         <v>400</v>
       </c>
       <c r="W13" s="36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="X13" s="36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Y13" s="36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Z13" s="36">
         <v>13</v>
       </c>
       <c r="AA13" s="36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AC13" s="17"/>
       <c r="AD13" s="17"/>
@@ -10244,10 +12941,10 @@
       <c r="AF13" s="17"/>
       <c r="AG13" s="19"/>
       <c r="AH13" s="35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AI13" s="35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AO13" s="8"/>
       <c r="AP13" s="8"/>
@@ -10258,10 +12955,10 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D14" s="8">
         <v>7</v>
@@ -10283,7 +12980,7 @@
         <v>7</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="30"/>
@@ -10304,7 +13001,7 @@
         <v>1000</v>
       </c>
       <c r="X14" s="37" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y14" s="36">
         <v>3</v>
@@ -10313,7 +13010,7 @@
         <v>17</v>
       </c>
       <c r="AA14" s="36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AC14" s="8">
         <v>1</v>
@@ -10322,19 +13019,19 @@
         <v>400</v>
       </c>
       <c r="AE14" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AF14" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG14" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AH14" s="8">
         <v>13</v>
       </c>
       <c r="AI14" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO14" s="8"/>
       <c r="AP14" s="8"/>
@@ -10345,10 +13042,10 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D15" s="8">
         <v>8</v>
@@ -10370,7 +13067,7 @@
         <v>8</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="30"/>
@@ -10412,7 +13109,7 @@
         <v>1</v>
       </c>
       <c r="AF15" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG15" s="8">
         <v>3</v>
@@ -10421,7 +13118,7 @@
         <v>17</v>
       </c>
       <c r="AI15" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO15" s="8"/>
       <c r="AP15" s="8"/>
@@ -10432,10 +13129,10 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D16" s="8">
         <v>9</v>
@@ -10457,7 +13154,7 @@
         <v>9</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M16" s="7"/>
       <c r="N16" s="30"/>
@@ -10519,10 +13216,10 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D17" s="8">
         <v>10</v>
@@ -10544,7 +13241,7 @@
         <v>10</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="30"/>
@@ -10606,10 +13303,10 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D18" s="8">
         <v>11</v>
@@ -10631,7 +13328,7 @@
         <v>11</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="30"/>
@@ -10693,10 +13390,10 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" s="8">
         <v>12</v>
@@ -10709,7 +13406,7 @@
         <v>6000000</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J19" s="36">
         <v>720</v>
@@ -10718,7 +13415,7 @@
         <v>12</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M19" s="7"/>
       <c r="N19" s="30"/>
@@ -10780,10 +13477,10 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D20" s="8">
         <v>13</v>
@@ -10796,7 +13493,7 @@
         <v>9000000</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J20" s="36">
         <v>777</v>
@@ -10805,7 +13502,7 @@
         <v>13</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M20" s="7"/>
       <c r="N20" s="30"/>
@@ -10867,10 +13564,10 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D21" s="8">
         <v>14</v>
@@ -10883,7 +13580,7 @@
         <v>12000000</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J21" s="36">
         <v>804</v>
@@ -10892,7 +13589,7 @@
         <v>14</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M21" s="7"/>
       <c r="N21" s="30"/>
@@ -10954,10 +13651,10 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D22" s="8">
         <v>15</v>
@@ -10970,7 +13667,7 @@
         <v>13000000</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J22" s="36">
         <v>831</v>
@@ -10979,7 +13676,7 @@
         <v>15</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="30"/>
@@ -11018,7 +13715,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="AE22" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF22" s="9" t="s">
         <v>82</v>
@@ -11041,10 +13738,10 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" s="8">
         <v>16</v>
@@ -11057,7 +13754,7 @@
         <v>15000000</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J23" s="36">
         <v>881</v>
@@ -11066,7 +13763,7 @@
         <v>16</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M23" s="7"/>
       <c r="N23" s="30"/>
@@ -11105,7 +13802,7 @@
         <v>5.5</v>
       </c>
       <c r="AE23" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF23" s="9" t="s">
         <v>91</v>
@@ -11128,10 +13825,10 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D24" s="8">
         <v>17</v>
@@ -11144,7 +13841,7 @@
         <v>16000000</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J24" s="36">
         <v>929</v>
@@ -11153,7 +13850,7 @@
         <v>17</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M24" s="7"/>
       <c r="N24" s="30"/>
@@ -11174,7 +13871,7 @@
         <v>6000000</v>
       </c>
       <c r="X24" s="37" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y24" s="36">
         <v>720</v>
@@ -11215,10 +13912,10 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D25" s="8">
         <v>18</v>
@@ -11231,7 +13928,7 @@
         <v>25000000</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J25" s="36">
         <v>1018</v>
@@ -11240,7 +13937,7 @@
         <v>18</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="30"/>
@@ -11261,7 +13958,7 @@
         <v>9000000</v>
       </c>
       <c r="X25" s="37" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y25" s="36">
         <v>777</v>
@@ -11279,10 +13976,10 @@
         <v>7.5</v>
       </c>
       <c r="AE25" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AF25" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG25" s="8">
         <v>720</v>
@@ -11312,7 +14009,7 @@
         <v>12000000</v>
       </c>
       <c r="X26" s="37" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y26" s="36">
         <v>804</v>
@@ -11330,10 +14027,10 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="AE26" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AF26" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG26" s="8">
         <v>777</v>
@@ -11359,7 +14056,7 @@
         <v>13000000</v>
       </c>
       <c r="X27" s="37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Y27" s="36">
         <v>831</v>
@@ -11377,10 +14074,10 @@
         <v>8.9</v>
       </c>
       <c r="AE27" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AF27" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG27" s="8">
         <v>804</v>
@@ -11406,7 +14103,7 @@
         <v>15000000</v>
       </c>
       <c r="X28" s="37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Y28" s="36">
         <v>881</v>
@@ -11427,7 +14124,7 @@
         <v>93</v>
       </c>
       <c r="AF28" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG28" s="8">
         <v>831</v>
@@ -11453,7 +14150,7 @@
         <v>16000000</v>
       </c>
       <c r="X29" s="37" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Y29" s="36">
         <v>929</v>
@@ -11471,10 +14168,10 @@
         <v>10</v>
       </c>
       <c r="AE29" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AF29" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG29" s="8">
         <v>881</v>
@@ -11500,7 +14197,7 @@
         <v>25000000</v>
       </c>
       <c r="X30" s="37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Y30" s="36">
         <v>1018</v>
@@ -11518,10 +14215,10 @@
         <v>10.4</v>
       </c>
       <c r="AE30" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF30" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG30" s="8">
         <v>929</v>
@@ -11544,10 +14241,10 @@
         <v>10.8</v>
       </c>
       <c r="AE31" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AF31" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG31" s="8">
         <v>1.018</v>
@@ -11591,7 +14288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27617101-733A-41D8-9344-27EF1469BD1C}">
   <dimension ref="A3:AQ30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11780,7 +14477,7 @@
         <v>2</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="30"/>
@@ -11873,7 +14570,7 @@
         <v>2</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="30"/>
@@ -11910,7 +14607,7 @@
         <v>3</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="30"/>
@@ -11956,7 +14653,7 @@
         <v>4</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M11" s="7"/>
       <c r="N11" s="30"/>
@@ -11996,7 +14693,7 @@
         <v>5</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="30"/>
@@ -12041,7 +14738,7 @@
         <v>6</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M13" s="7"/>
       <c r="N13" s="30"/>
@@ -12086,7 +14783,7 @@
         <v>7</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="30"/>
@@ -12131,7 +14828,7 @@
         <v>8</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="30"/>
@@ -12176,7 +14873,7 @@
         <v>9</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M16" s="7"/>
       <c r="N16" s="30"/>
@@ -12221,7 +14918,7 @@
         <v>9</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="30"/>
@@ -12266,7 +14963,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="30"/>
@@ -12311,7 +15008,7 @@
         <v>11</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M19" s="7"/>
       <c r="N19" s="30"/>
@@ -12356,7 +15053,7 @@
         <v>12</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M20" s="7"/>
       <c r="N20" s="30"/>
@@ -12401,7 +15098,7 @@
         <v>13</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M21" s="7"/>
       <c r="N21" s="30"/>
@@ -12446,7 +15143,7 @@
         <v>14</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="30"/>
@@ -12491,7 +15188,7 @@
         <v>15</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M23" s="7"/>
       <c r="N23" s="30"/>
@@ -12536,7 +15233,7 @@
         <v>16</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M24" s="7"/>
       <c r="N24" s="30"/>
@@ -12581,7 +15278,7 @@
         <v>17</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="30"/>
@@ -12622,7 +15319,7 @@
         <v>18</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R26">
         <f t="shared" si="0"/>
@@ -12701,7 +15398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1985FBF0-AEF2-4861-8D8E-4DCFDFFB41E6}">
   <dimension ref="A3:AM25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13931,7 +16628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39BC1346-2BF0-4921-9BE2-468AE4CA80E7}">
   <dimension ref="A3:AL28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -15330,7 +18027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA69B0F-3FCE-4DFB-B093-D47425828D68}">
   <dimension ref="A3:AL28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
